--- a/data/trans_orig/P5711-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5711-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2007</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>493927</t>
+          <t>495134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>540250</t>
+          <t>542204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>391650</t>
+          <t>386862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>442568</t>
+          <t>439776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>895562</t>
+          <t>898183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>966668</t>
+          <t>971885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>96009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134590</t>
+          <t>134868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145623</t>
+          <t>145324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189652</t>
+          <t>188912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252159</t>
+          <t>253337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>315151</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>39192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>64539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73224</t>
+          <t>72596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>88508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126374</t>
+          <t>129337</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27167</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51232</t>
+          <t>52661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61015</t>
+          <t>62512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>627495</t>
+          <t>626282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>687243</t>
+          <t>685841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>569348</t>
+          <t>568437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>633064</t>
+          <t>629156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1214133</t>
+          <t>1212266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1295884</t>
+          <t>1297392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176124</t>
+          <t>176840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229409</t>
+          <t>230018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189276</t>
+          <t>190197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>243095</t>
+          <t>244862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385481</t>
+          <t>385768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456195</t>
+          <t>460162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59302</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94181</t>
+          <t>95608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78696</t>
+          <t>78428</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116138</t>
+          <t>116337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145814</t>
+          <t>145624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197706</t>
+          <t>196467</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58601</t>
+          <t>60517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48384</t>
+          <t>49373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81360</t>
+          <t>82203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>478880</t>
+          <t>477398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>526768</t>
+          <t>524639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423284</t>
+          <t>424281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>471625</t>
+          <t>471184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>913641</t>
+          <t>915091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>983247</t>
+          <t>983122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91577</t>
+          <t>91381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129636</t>
+          <t>131702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119312</t>
+          <t>120690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160446</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221665</t>
+          <t>220884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279045</t>
+          <t>280455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>55767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49796</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81156</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86953</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127772</t>
+          <t>127477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36651</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64480</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>593324</t>
+          <t>594884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>648716</t>
+          <t>649634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>606049</t>
+          <t>606137</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>666116</t>
+          <t>664174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1213417</t>
+          <t>1213756</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1296823</t>
+          <t>1302824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191260</t>
+          <t>190951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240434</t>
+          <t>240127</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202932</t>
+          <t>203871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253738</t>
+          <t>255039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408239</t>
+          <t>406910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480982</t>
+          <t>480743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>52901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84453</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86680</t>
+          <t>85833</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126795</t>
+          <t>124054</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>147245</t>
+          <t>149803</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>198521</t>
+          <t>199980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>44706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44627</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>76110</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73344</t>
+          <t>74361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113051</t>
+          <t>112072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22706</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2242880</t>
+          <t>2243506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2348830</t>
+          <t>2350593</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2035771</t>
+          <t>2042485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2152681</t>
+          <t>2153914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4320224</t>
+          <t>4314785</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4480472</t>
+          <t>4471263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>596519</t>
+          <t>598204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>689805</t>
+          <t>690294</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>702449</t>
+          <t>697462</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>800660</t>
+          <t>794675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1328839</t>
+          <t>1326863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1457283</t>
+          <t>1463458</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>208609</t>
+          <t>206025</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>266064</t>
+          <t>266017</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289324</t>
+          <t>288990</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>357349</t>
+          <t>355428</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>509560</t>
+          <t>508775</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>601020</t>
+          <t>599422</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>62771</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>100777</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146670</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>198190</t>
+          <t>199198</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>218695</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>283495</t>
+          <t>284170</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76898</t>
+          <t>76747</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2012</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500041</t>
+          <t>499285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>550313</t>
+          <t>550076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>462029</t>
+          <t>462630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>509797</t>
+          <t>512592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>979736</t>
+          <t>981220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1048050</t>
+          <t>1050508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110610</t>
+          <t>110957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157697</t>
+          <t>157567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142170</t>
+          <t>140728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187668</t>
+          <t>186602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267881</t>
+          <t>267226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>331531</t>
+          <t>330258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45742</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,47 +4616,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>24286</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16065</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37151</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24286</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15817</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35856</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44588</t>
+          <t>43568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76063</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32623</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>683221</t>
+          <t>680780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>744017</t>
+          <t>746341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>636689</t>
+          <t>643261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>702138</t>
+          <t>707799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1344668</t>
+          <t>1347212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1433315</t>
+          <t>1437205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198123</t>
+          <t>197087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253482</t>
+          <t>254871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235220</t>
+          <t>228559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291714</t>
+          <t>287811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447161</t>
+          <t>441384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>528192</t>
+          <t>526507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71724</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90461</t>
+          <t>92223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106705</t>
+          <t>106195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153186</t>
+          <t>151531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>548551</t>
+          <t>550301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>600367</t>
+          <t>598563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513490</t>
+          <t>513347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>567100</t>
+          <t>566365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1080021</t>
+          <t>1078327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154102</t>
+          <t>1152519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92386</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132764</t>
+          <t>131342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>118272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162235</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221179</t>
+          <t>222230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285592</t>
+          <t>281213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72686</t>
+          <t>73916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>50327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84148</t>
+          <t>84371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99964</t>
+          <t>99831</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144074</t>
+          <t>144857</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>619316</t>
+          <t>621039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>678554</t>
+          <t>680083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>642533</t>
+          <t>641477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>705000</t>
+          <t>704302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1278686</t>
+          <t>1284988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1364606</t>
+          <t>1365980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>187105</t>
+          <t>184802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241400</t>
+          <t>237864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>234103</t>
+          <t>233101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290067</t>
+          <t>294625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439966</t>
+          <t>436089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>520387</t>
+          <t>511956</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52180</t>
+          <t>52797</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86948</t>
+          <t>85650</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61108</t>
+          <t>60362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>95366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121974</t>
+          <t>120578</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>168418</t>
+          <t>167377</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,47 +6775,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>20248</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>12794</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>31372</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>20248</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>12847</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>31854</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2409691</t>
+          <t>2409627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2519909</t>
+          <t>2523903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2317403</t>
+          <t>2314280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2431950</t>
+          <t>2430643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4766664</t>
+          <t>4766522</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4925920</t>
+          <t>4924672</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>631435</t>
+          <t>630256</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>727549</t>
+          <t>731276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>773429</t>
+          <t>778233</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>878920</t>
+          <t>885891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443246</t>
+          <t>1439943</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1584947</t>
+          <t>1583088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187471</t>
+          <t>183490</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>244913</t>
+          <t>242508</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207793</t>
+          <t>207357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>269345</t>
+          <t>269074</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>409447</t>
+          <t>410320</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>493628</t>
+          <t>495511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30953</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57586</t>
+          <t>57852</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>62234</t>
+          <t>60696</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>99405</t>
+          <t>98880</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>98076</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>143662</t>
+          <t>146200</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>42831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2016</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373274</t>
+          <t>374203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>425107</t>
+          <t>422982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334293</t>
+          <t>335848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>385691</t>
+          <t>389323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>726794</t>
+          <t>715583</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>802207</t>
+          <t>792284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189200</t>
+          <t>193418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237705</t>
+          <t>239644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197566</t>
+          <t>199645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246378</t>
+          <t>246292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>401769</t>
+          <t>406642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471028</t>
+          <t>472985</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36334</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64565</t>
+          <t>63214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83201</t>
+          <t>83708</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95365</t>
+          <t>95114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136961</t>
+          <t>135226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>565520</t>
+          <t>562728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>631006</t>
+          <t>624622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>555195</t>
+          <t>553274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>621940</t>
+          <t>621816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1136264</t>
+          <t>1143442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1227617</t>
+          <t>1232781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297669</t>
+          <t>298900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>360730</t>
+          <t>361979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316258</t>
+          <t>314582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378219</t>
+          <t>378851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632471</t>
+          <t>632086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>721105</t>
+          <t>718940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>63034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103156</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102839</t>
+          <t>102608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141945</t>
+          <t>137525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>190101</t>
+          <t>187890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,47 +9088,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>31648</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>21814</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>45417</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>31648</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>44302</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,44 +9171,44 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4886</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10678</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4886</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11353</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331288</t>
+          <t>332618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>389388</t>
+          <t>389858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293355</t>
+          <t>292128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>348578</t>
+          <t>346950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>640291</t>
+          <t>638420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>721061</t>
+          <t>716503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280110</t>
+          <t>275347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334221</t>
+          <t>331063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306497</t>
+          <t>304237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>361614</t>
+          <t>360826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>595661</t>
+          <t>599427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>675052</t>
+          <t>680767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71661</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108000</t>
+          <t>109561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90716</t>
+          <t>92917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130108</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174290</t>
+          <t>175416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>227771</t>
+          <t>229018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29255</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9868,62 +9868,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5870</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5239</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>554520</t>
+          <t>553688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>615328</t>
+          <t>612440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>574079</t>
+          <t>575370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>644252</t>
+          <t>642319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1143453</t>
+          <t>1147385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1233936</t>
+          <t>1239156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222999</t>
+          <t>224448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278304</t>
+          <t>278334</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254211</t>
+          <t>247078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316990</t>
+          <t>309759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>494139</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>572459</t>
+          <t>570894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>56027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88152</t>
+          <t>88440</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90334</t>
+          <t>91874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>131794</t>
+          <t>132886</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158266</t>
+          <t>156768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>210933</t>
+          <t>210224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28041</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22620</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>37122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68454</t>
+          <t>67841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1873518</t>
+          <t>1873544</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2000375</t>
+          <t>1997217</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1817290</t>
+          <t>1820415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1941673</t>
+          <t>1940141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3731300</t>
+          <t>3736353</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3905598</t>
+          <t>3906052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1044923</t>
+          <t>1043904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1156610</t>
+          <t>1151257</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1125297</t>
+          <t>1129350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1242584</t>
+          <t>1239967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2206854</t>
+          <t>2201477</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2362074</t>
+          <t>2356744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258158</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>325214</t>
+          <t>330236</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>336433</t>
+          <t>334844</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>409072</t>
+          <t>410829</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>614591</t>
+          <t>610287</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>709036</t>
+          <t>708794</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>63652</t>
+          <t>64785</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>102166</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>106967</t>
+          <t>103537</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>152995</t>
+          <t>150666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,82 +11212,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>24293</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>16131</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>35810</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>42748</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>31571</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>59156</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>24293</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>15539</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>35529</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>42748</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>31880</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>57353</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2023</t>
+          <t>Población según la frecuencia de recibir ayuda cuando se está enfermo en la cama en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>349898</t>
+          <t>347108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403167</t>
+          <t>400985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354525</t>
+          <t>353818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>393832</t>
+          <t>394543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>716371</t>
+          <t>716842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>787628</t>
+          <t>781727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137947</t>
+          <t>140790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184116</t>
+          <t>184771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180101</t>
+          <t>179431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217232</t>
+          <t>215039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>329610</t>
+          <t>329311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387857</t>
+          <t>385975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>64663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46932</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66557</t>
+          <t>65965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88837</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122159</t>
+          <t>122835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>74930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>649330</t>
+          <t>645881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>962605</t>
+          <t>995337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>476370</t>
+          <t>476503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>529175</t>
+          <t>529444</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1148566</t>
+          <t>1146569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1577786</t>
+          <t>1581567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176246</t>
+          <t>145669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413194</t>
+          <t>412939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305163</t>
+          <t>304245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353444</t>
+          <t>354357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423367</t>
+          <t>436250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>737892</t>
+          <t>742897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>37504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105150</t>
+          <t>103455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58295</t>
+          <t>59098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83332</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>89725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>177629</t>
+          <t>176930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53279</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80746</t>
+          <t>80697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>396233</t>
+          <t>395720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>453134</t>
+          <t>455401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>230636</t>
+          <t>197778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>577166</t>
+          <t>576716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>594248</t>
+          <t>562746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1009156</t>
+          <t>1007692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177763</t>
+          <t>176172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230638</t>
+          <t>230364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107990</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>284371</t>
+          <t>279257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265607</t>
+          <t>248230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>489448</t>
+          <t>485974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46631</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78654</t>
+          <t>79921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65770</t>
+          <t>65717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>580569</t>
+          <t>621511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123815</t>
+          <t>124534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>759621</t>
+          <t>847277</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>556317</t>
+          <t>556548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>618536</t>
+          <t>615277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>661047</t>
+          <t>661610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>779567</t>
+          <t>778082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1238108</t>
+          <t>1233586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1367831</t>
+          <t>1365936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205662</t>
+          <t>205242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256643</t>
+          <t>258513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>219990</t>
+          <t>219933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304179</t>
+          <t>302004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>440692</t>
+          <t>446826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>541921</t>
+          <t>544731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>49273</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78639</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74158</t>
+          <t>74286</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>101922</t>
+          <t>104750</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143321</t>
+          <t>144026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52438</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53798</t>
+          <t>53557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>80916</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2031282</t>
+          <t>2040249</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2438452</t>
+          <t>2454057</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1678614</t>
+          <t>1658342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2167900</t>
+          <t>2161876</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3829940</t>
+          <t>3745819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4455395</t>
+          <t>4443923</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>708008</t>
+          <t>705768</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>999322</t>
+          <t>998804</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>834501</t>
+          <t>814302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1100422</t>
+          <t>1092493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1651531</t>
+          <t>1694416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2054314</t>
+          <t>2057555</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>191750</t>
+          <t>189415</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>290612</t>
+          <t>284681</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>248364</t>
+          <t>249175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1079436</t>
+          <t>1015834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>488975</t>
+          <t>483887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1485051</t>
+          <t>1426021</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68274</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>111375</t>
+          <t>114048</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106924</t>
+          <t>102301</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>151444</t>
+          <t>151166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>186992</t>
+          <t>182581</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>247818</t>
+          <t>247010</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>54560</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56209</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70209</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103158</t>
+          <t>104074</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5711-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5711-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>495134</t>
+          <t>496008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>542204</t>
+          <t>539451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>386862</t>
+          <t>390186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>439776</t>
+          <t>440297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>898183</t>
+          <t>901447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>971885</t>
+          <t>967573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96009</t>
+          <t>98134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134868</t>
+          <t>134902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145324</t>
+          <t>142041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188912</t>
+          <t>189013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253337</t>
+          <t>256008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314372</t>
+          <t>311690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>39280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64539</t>
+          <t>65804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>71867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88508</t>
+          <t>88137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>129337</t>
+          <t>129899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>62725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>626282</t>
+          <t>626124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>685841</t>
+          <t>685932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>568437</t>
+          <t>564031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>629156</t>
+          <t>629347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1212266</t>
+          <t>1214844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1297392</t>
+          <t>1302300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176840</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230018</t>
+          <t>233749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>190197</t>
+          <t>190586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244862</t>
+          <t>243265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385768</t>
+          <t>383962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>460162</t>
+          <t>453463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59088</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>93369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,47 +1656,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>96348</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>78595</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>116814</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>9,95%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>96348</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>78428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116337</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>147472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>196467</t>
+          <t>195866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49373</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82203</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>477398</t>
+          <t>479592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524639</t>
+          <t>525583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>424281</t>
+          <t>423233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>471184</t>
+          <t>470739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>915091</t>
+          <t>913468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>983122</t>
+          <t>984686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91381</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131702</t>
+          <t>130579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120690</t>
+          <t>120436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>161509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220884</t>
+          <t>219693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280455</t>
+          <t>277782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29466</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>57926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79959</t>
+          <t>82075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87317</t>
+          <t>88145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127477</t>
+          <t>126912</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19290</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39196</t>
+          <t>39683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65227</t>
+          <t>64640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>594884</t>
+          <t>591562</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>649634</t>
+          <t>648687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>606137</t>
+          <t>602677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>664174</t>
+          <t>663823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1213756</t>
+          <t>1215303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1302824</t>
+          <t>1299829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190951</t>
+          <t>189946</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240127</t>
+          <t>239799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>203871</t>
+          <t>200414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>256123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406910</t>
+          <t>402554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480743</t>
+          <t>478081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52901</t>
+          <t>53524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82852</t>
+          <t>85027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85833</t>
+          <t>86256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124054</t>
+          <t>126381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149803</t>
+          <t>146766</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199980</t>
+          <t>195919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>45933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>44496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76110</t>
+          <t>77222</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74361</t>
+          <t>73767</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112072</t>
+          <t>111198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2243506</t>
+          <t>2243389</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2350593</t>
+          <t>2350168</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2042485</t>
+          <t>2042091</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2153914</t>
+          <t>2149664</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4314785</t>
+          <t>4319479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4471263</t>
+          <t>4478697</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>598204</t>
+          <t>597867</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>690294</t>
+          <t>691012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>697462</t>
+          <t>702051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>794675</t>
+          <t>800361</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1326863</t>
+          <t>1323102</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1463458</t>
+          <t>1451930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>206025</t>
+          <t>204900</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>266017</t>
+          <t>265395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>288990</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>355428</t>
+          <t>353704</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>508775</t>
+          <t>514428</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>599422</t>
+          <t>604712</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62771</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100777</t>
+          <t>101024</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146346</t>
+          <t>145394</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>199198</t>
+          <t>198980</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>218446</t>
+          <t>220858</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>284170</t>
+          <t>285009</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>77321</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>499285</t>
+          <t>502410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>550076</t>
+          <t>550144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>462630</t>
+          <t>459453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>512592</t>
+          <t>512118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981220</t>
+          <t>976334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1050508</t>
+          <t>1046323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110957</t>
+          <t>112183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157567</t>
+          <t>156065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140728</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186602</t>
+          <t>192071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267226</t>
+          <t>267632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>330258</t>
+          <t>330992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>46459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43568</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72553</t>
+          <t>74374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>30131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>680780</t>
+          <t>681759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>746341</t>
+          <t>744825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643261</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>707799</t>
+          <t>704875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1347212</t>
+          <t>1350196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1437205</t>
+          <t>1437090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,24%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197087</t>
+          <t>194833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254871</t>
+          <t>251857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228559</t>
+          <t>233958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287811</t>
+          <t>291772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441384</t>
+          <t>442781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>526507</t>
+          <t>524892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71458</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92223</t>
+          <t>90147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106195</t>
+          <t>105888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151531</t>
+          <t>150984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50101</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550301</t>
+          <t>547366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>598563</t>
+          <t>599016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513347</t>
+          <t>515884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>566365</t>
+          <t>570423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1078327</t>
+          <t>1080339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1152519</t>
+          <t>1153232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>91519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131342</t>
+          <t>133765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118272</t>
+          <t>117256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162899</t>
+          <t>163107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222230</t>
+          <t>221132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281213</t>
+          <t>282025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41242</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73916</t>
+          <t>73556</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>83419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99831</t>
+          <t>98799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144857</t>
+          <t>144038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>47546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>621039</t>
+          <t>619077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>680083</t>
+          <t>680688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>641477</t>
+          <t>638621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>704302</t>
+          <t>702453</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1284988</t>
+          <t>1285229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1365980</t>
+          <t>1368071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184802</t>
+          <t>185263</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237864</t>
+          <t>238871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>233101</t>
+          <t>237901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294625</t>
+          <t>294511</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436089</t>
+          <t>437387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511956</t>
+          <t>513692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52797</t>
+          <t>54641</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85650</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60362</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95366</t>
+          <t>97096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120578</t>
+          <t>122696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>167377</t>
+          <t>167805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>24740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2409627</t>
+          <t>2411503</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2523903</t>
+          <t>2523902</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2314280</t>
+          <t>2318575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2430643</t>
+          <t>2441322</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4766522</t>
+          <t>4759246</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4924672</t>
+          <t>4924031</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>630256</t>
+          <t>632873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>731276</t>
+          <t>729780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>778233</t>
+          <t>771971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>885891</t>
+          <t>880804</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1439943</t>
+          <t>1439837</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1583088</t>
+          <t>1583406</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>183490</t>
+          <t>184460</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>242508</t>
+          <t>245766</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>207357</t>
+          <t>208375</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>269074</t>
+          <t>272041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>410320</t>
+          <t>407772</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>495511</t>
+          <t>498494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57852</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>97346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100031</t>
+          <t>100836</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>146200</t>
+          <t>145617</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42831</t>
+          <t>44393</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>374203</t>
+          <t>372582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>422982</t>
+          <t>423716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>335848</t>
+          <t>333177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389323</t>
+          <t>386715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>715583</t>
+          <t>717139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>792284</t>
+          <t>791872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193418</t>
+          <t>190658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239644</t>
+          <t>239745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199645</t>
+          <t>199692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246292</t>
+          <t>247105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406642</t>
+          <t>406524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472985</t>
+          <t>476692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63214</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83708</t>
+          <t>85553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>93657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>134753</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>35640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>562728</t>
+          <t>563163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>624622</t>
+          <t>628979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>553274</t>
+          <t>558067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>621816</t>
+          <t>620215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1143442</t>
+          <t>1136173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1232781</t>
+          <t>1230375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298900</t>
+          <t>297972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361979</t>
+          <t>357628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314582</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378851</t>
+          <t>377249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632086</t>
+          <t>634462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718940</t>
+          <t>722832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100246</t>
+          <t>100497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>65270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102608</t>
+          <t>101224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137525</t>
+          <t>139552</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>187890</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>332618</t>
+          <t>331450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>389858</t>
+          <t>393054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292128</t>
+          <t>291563</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>346950</t>
+          <t>347170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>638420</t>
+          <t>641188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>716503</t>
+          <t>721502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275347</t>
+          <t>276563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331063</t>
+          <t>332950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304237</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360826</t>
+          <t>359703</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>599427</t>
+          <t>597417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>680767</t>
+          <t>678117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72671</t>
+          <t>71003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109561</t>
+          <t>107747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92917</t>
+          <t>89716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>132494</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>175416</t>
+          <t>171841</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>229018</t>
+          <t>231066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30868</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>553688</t>
+          <t>552434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>612440</t>
+          <t>611580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>575370</t>
+          <t>575000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>642319</t>
+          <t>637678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1147385</t>
+          <t>1147535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1239156</t>
+          <t>1238900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>224448</t>
+          <t>224212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278334</t>
+          <t>278873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247078</t>
+          <t>255786</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309759</t>
+          <t>312162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>489146</t>
+          <t>491039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>570894</t>
+          <t>574257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56027</t>
+          <t>58054</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88440</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132886</t>
+          <t>131310</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156768</t>
+          <t>158690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>210224</t>
+          <t>212103</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37122</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67841</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1873544</t>
+          <t>1883759</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1997217</t>
+          <t>2000314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1820415</t>
+          <t>1822524</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1940141</t>
+          <t>1940338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3736353</t>
+          <t>3733092</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3906052</t>
+          <t>3903002</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1043904</t>
+          <t>1043947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1151257</t>
+          <t>1156443</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1129350</t>
+          <t>1126512</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1239967</t>
+          <t>1238404</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2201477</t>
+          <t>2201557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2356744</t>
+          <t>2362393</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>256746</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>330236</t>
+          <t>326235</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>334844</t>
+          <t>336064</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>410829</t>
+          <t>407486</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>610287</t>
+          <t>611981</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>708794</t>
+          <t>709773</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64785</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100401</t>
+          <t>101786</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,47 +11134,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>126791</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>105335</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>150975</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>126791</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>103537</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>150666</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,47 +11247,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>42748</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>32172</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>57248</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>42748</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>31571</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>59156</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>375891</t>
+          <t>398586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>347108</t>
+          <t>369376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>400985</t>
+          <t>423788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>374203</t>
+          <t>404362</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353818</t>
+          <t>384491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>394543</t>
+          <t>426603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>750094</t>
+          <t>802948</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>716842</t>
+          <t>766777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>781727</t>
+          <t>838410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160948</t>
+          <t>181849</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140790</t>
+          <t>159386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184771</t>
+          <t>207861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>197260</t>
+          <t>216076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179431</t>
+          <t>197366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215039</t>
+          <t>236687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>358208</t>
+          <t>397925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>329311</t>
+          <t>367440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>385975</t>
+          <t>428980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48809</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64663</t>
+          <t>71709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56081</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>49030</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>104890</t>
+          <t>114437</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>97303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122835</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -11993,17 +11993,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31868</t>
+          <t>34285</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40944</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,27 +12063,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60704</t>
+          <t>65593</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49255</t>
+          <t>52327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74930</t>
+          <t>81316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>26019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>631956</t>
+          <t>687173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>631956</t>
+          <t>687173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>631956</t>
+          <t>687173</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>672420</t>
+          <t>729644</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672420</t>
+          <t>729644</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>672420</t>
+          <t>729644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1304375</t>
+          <t>1416817</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1304375</t>
+          <t>1416817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1304375</t>
+          <t>1416817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>769672</t>
+          <t>578761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>645881</t>
+          <t>541938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>995337</t>
+          <t>616635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>503035</t>
+          <t>549624</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>476503</t>
+          <t>520419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>529444</t>
+          <t>579205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1272707</t>
+          <t>1128385</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1146569</t>
+          <t>1081414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1581567</t>
+          <t>1173259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>315762</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145669</t>
+          <t>315834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>412939</t>
+          <t>386331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>327621</t>
+          <t>374904</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304245</t>
+          <t>347849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354357</t>
+          <t>401061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>643383</t>
+          <t>724904</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436250</t>
+          <t>680960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>742897</t>
+          <t>765447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72962</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37504</t>
+          <t>61059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70924</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>66500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85512</t>
+          <t>95613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>143886</t>
+          <t>157396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>138690</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176930</t>
+          <t>183312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42250</t>
+          <t>49693</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64909</t>
+          <t>76352</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>62402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80697</t>
+          <t>92013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>39942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1191660</t>
+          <t>1047675</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1191660</t>
+          <t>1047675</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1191660</t>
+          <t>1047675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>954941</t>
+          <t>1067537</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>954941</t>
+          <t>1067537</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>954941</t>
+          <t>1067537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2146601</t>
+          <t>2115212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2146601</t>
+          <t>2115212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2146601</t>
+          <t>2115212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>425895</t>
+          <t>474736</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>395720</t>
+          <t>442069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>455401</t>
+          <t>508087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>439740</t>
+          <t>475121</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197778</t>
+          <t>448127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>576716</t>
+          <t>501527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>865636</t>
+          <t>949857</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>562746</t>
+          <t>907446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1007692</t>
+          <t>992923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>201400</t>
+          <t>231518</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>176172</t>
+          <t>203052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230364</t>
+          <t>260854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>210529</t>
+          <t>244131</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100568</t>
+          <t>221807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>279257</t>
+          <t>269448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>411929</t>
+          <t>475648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248230</t>
+          <t>439000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>485974</t>
+          <t>517009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>77701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79921</t>
+          <t>99640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>260739</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65717</t>
+          <t>53889</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>621511</t>
+          <t>83212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,22 +13314,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>321715</t>
+          <t>145306</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124534</t>
+          <t>122766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>847277</t>
+          <t>173090</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19684</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703394</t>
+          <t>801704</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703394</t>
+          <t>801704</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703394</t>
+          <t>801704</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1636195</t>
+          <t>1613367</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1636195</t>
+          <t>1613367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1636195</t>
+          <t>1613367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>587198</t>
+          <t>616840</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>556548</t>
+          <t>585685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>615277</t>
+          <t>647383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>698852</t>
+          <t>671300</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>661610</t>
+          <t>642453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>778082</t>
+          <t>697527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1286051</t>
+          <t>1288141</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1233586</t>
+          <t>1244965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1365936</t>
+          <t>1332538</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>230774</t>
+          <t>251454</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205242</t>
+          <t>222864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258513</t>
+          <t>276665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>271626</t>
+          <t>302422</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>219933</t>
+          <t>276500</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302004</t>
+          <t>326366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>502400</t>
+          <t>553876</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>446826</t>
+          <t>516379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>544731</t>
+          <t>592962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78279</t>
+          <t>86646</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60503</t>
+          <t>68549</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>55844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>85007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>138809</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>119513</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144026</t>
+          <t>159241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>41447</t>
+          <t>49127</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30702</t>
+          <t>39634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>80300</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53557</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80916</t>
+          <t>96925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -14152,22 +14152,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>918172</t>
+          <t>981963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>918172</t>
+          <t>981963</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>918172</t>
+          <t>981963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1084080</t>
+          <t>1107764</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1084080</t>
+          <t>1107764</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1084080</t>
+          <t>1107764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2002253</t>
+          <t>2089727</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2002253</t>
+          <t>2089727</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2002253</t>
+          <t>2089727</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2158657</t>
+          <t>2068923</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2040249</t>
+          <t>2007019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2454057</t>
+          <t>2134268</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2015831</t>
+          <t>2100407</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1658342</t>
+          <t>2049918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2161876</t>
+          <t>2159615</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4174488</t>
+          <t>4169331</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3745819</t>
+          <t>4083635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4443923</t>
+          <t>4246221</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>908883</t>
+          <t>1014821</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>705768</t>
+          <t>954709</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>998804</t>
+          <t>1073951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1007036</t>
+          <t>1137531</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>814302</t>
+          <t>1084406</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1092493</t>
+          <t>1185752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1915920</t>
+          <t>2152353</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1694416</t>
+          <t>2080058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2057555</t>
+          <t>2233473</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -14608,102 +14608,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>245596</t>
+          <t>280208</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189415</t>
+          <t>247988</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>284681</t>
+          <t>318219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>275740</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>248882</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>303690</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>555948</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>515443</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>597592</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>448247</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>249175</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1015834</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>693844</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>483887</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1426021</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>90687</t>
+          <t>105243</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>70584</t>
+          <t>87189</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>126107</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>129270</t>
+          <t>147855</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>102301</t>
+          <t>130549</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>151166</t>
+          <t>170826</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>219957</t>
+          <t>253099</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>182581</t>
+          <t>226569</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>247010</t>
+          <t>283534</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33757</t>
+          <t>44005</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>69458</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>85214</t>
+          <t>104392</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69317</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104074</t>
+          <t>124568</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3445182</t>
+          <t>3518515</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3445182</t>
+          <t>3518515</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3445182</t>
+          <t>3518515</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3644241</t>
+          <t>3716607</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3644241</t>
+          <t>3716607</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3644241</t>
+          <t>3716607</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7089423</t>
+          <t>7235123</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7089423</t>
+          <t>7235123</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7089423</t>
+          <t>7235123</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
